--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6263-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6263-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B2ED286-662E-425C-B675-92C664F95505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{40FA353E-4EA6-4650-A06E-545F1B86AC61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{2B16254A-AFF4-4EA3-8220-149200B3F068}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{C4245B6E-53B3-4480-BA05-E10BFFC7CAB0}"/>
   </bookViews>
   <sheets>
     <sheet name="6263-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1475,24 +1475,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42108E9A-D2C9-4F58-B8CC-DF720521D607}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AEAD712-EACE-456A-95C3-CDA53FF97F22}">
   <dimension ref="A1:X30"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="13" width="6.25" customWidth="1"/>
-    <col min="14" max="15" width="6.625" customWidth="1"/>
-    <col min="16" max="18" width="6.25" customWidth="1"/>
-    <col min="19" max="19" width="6.625" customWidth="1"/>
-    <col min="20" max="20" width="6.25" customWidth="1"/>
-    <col min="21" max="21" width="6.625" customWidth="1"/>
-    <col min="22" max="22" width="6.25" customWidth="1"/>
-    <col min="23" max="23" width="6.625" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1526,7 +1525,7 @@
       <c r="W1" s="26"/>
       <c r="X1" s="18"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
@@ -1562,7 +1561,7 @@
       <c r="W2" s="28"/>
       <c r="X2" s="29"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
         <v>2</v>
       </c>
@@ -1614,7 +1613,7 @@
       </c>
       <c r="X3" s="32"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="21"/>
       <c r="B4" s="22"/>
       <c r="C4" s="7"/>
@@ -1682,7 +1681,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="33">
         <v>2024</v>
       </c>
@@ -1754,7 +1753,7 @@
         <v>6.42</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="35">
         <v>2023</v>
       </c>
@@ -1826,7 +1825,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="33">
         <v>2022</v>
       </c>
@@ -1898,7 +1897,7 @@
         <v>7.48</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="35">
         <v>2021</v>
       </c>
@@ -1970,7 +1969,7 @@
         <v>6.87</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="33">
         <v>2020</v>
       </c>
@@ -2042,7 +2041,7 @@
         <v>6.57</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2019</v>
       </c>
@@ -2114,7 +2113,7 @@
         <v>8.82</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="33">
         <v>2018</v>
       </c>
@@ -2186,7 +2185,7 @@
         <v>7.61</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="35">
         <v>2017</v>
       </c>
@@ -2258,7 +2257,7 @@
         <v>8.19</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="33">
         <v>2016</v>
       </c>
@@ -2330,7 +2329,7 @@
         <v>8.4499999999999993</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="35">
         <v>2015</v>
       </c>
@@ -2402,7 +2401,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="33">
         <v>2014</v>
       </c>
@@ -2474,7 +2473,7 @@
         <v>9.74</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>2013</v>
       </c>
@@ -2546,7 +2545,7 @@
         <v>7.39</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="33">
         <v>2012</v>
       </c>
@@ -2618,7 +2617,7 @@
         <v>8.98</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="35">
         <v>2011</v>
       </c>
@@ -2690,7 +2689,7 @@
         <v>8.07</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="33">
         <v>2010</v>
       </c>
@@ -2762,7 +2761,7 @@
         <v>9.49</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="35">
         <v>2009</v>
       </c>
@@ -2834,7 +2833,7 @@
         <v>7.02</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="33">
         <v>2008</v>
       </c>
@@ -2906,7 +2905,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="35">
         <v>2007</v>
       </c>
@@ -2978,7 +2977,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="33">
         <v>2006</v>
       </c>
@@ -3050,7 +3049,7 @@
         <v>9.76</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="35">
         <v>2005</v>
       </c>
@@ -3122,7 +3121,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="33">
         <v>2004</v>
       </c>
@@ -3194,7 +3193,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="35">
         <v>2003</v>
       </c>
@@ -3266,7 +3265,7 @@
         <v>7.74</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="33">
         <v>2002</v>
       </c>
@@ -3338,7 +3337,7 @@
         <v>6.71</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="35">
         <v>2001</v>
       </c>
@@ -3410,7 +3409,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="33">
         <v>2000</v>
       </c>
@@ -3482,7 +3481,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="35" t="s">
         <v>51</v>
       </c>
